--- a/data/trans_bre/IQ2601_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-4,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-3,75%</t>
+          <t>-5,59%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 13,86</t>
+          <t>-7,81; 12,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 23,97</t>
+          <t>-2,71; 21,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 0,62</t>
+          <t>-24,05; 0,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 15,02</t>
+          <t>-23,57; 13,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 22,76</t>
+          <t>-10,78; 20,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 59,61</t>
+          <t>-4,86; 52,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 1,12</t>
+          <t>-32,82; -0,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 20,52</t>
+          <t>-27,21; 18,51</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-16,26</t>
+          <t>-16,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,88%</t>
+          <t>-21,57%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 13,79</t>
+          <t>-7,75; 12,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 25,14</t>
+          <t>3,31; 24,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 19,6</t>
+          <t>-0,91; 20,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,7; 6,32</t>
+          <t>-37,62; 4,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 20,3</t>
+          <t>-9,99; 18,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 52,72</t>
+          <t>5,57; 53,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 38,02</t>
+          <t>-1,4; 37,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 9,45</t>
+          <t>-44,91; 6,3</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>11,83</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 14,92</t>
+          <t>-8,6; 15,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 12,91</t>
+          <t>-12,97; 13,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,22; -3,12</t>
+          <t>-29,54; -3,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 44,71</t>
+          <t>-24,99; 39,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 25,94</t>
+          <t>-12,56; 28,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 30,92</t>
+          <t>-22,81; 32,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -4,38</t>
+          <t>-38,62; -5,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 147,76</t>
+          <t>-40,67; 113,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 15,54</t>
+          <t>0,79; 15,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 8,74</t>
+          <t>-6,21; 9,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 5,3</t>
+          <t>-8,25; 6,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 18,83</t>
+          <t>-14,91; 17,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 26,56</t>
+          <t>1,07; 25,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 19,38</t>
+          <t>-11,94; 22,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 8,45</t>
+          <t>-11,96; 10,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 28,0</t>
+          <t>-18,54; 26,67</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,41</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 15,29</t>
+          <t>-4,84; 14,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 7,91</t>
+          <t>-12,07; 7,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 11,6</t>
+          <t>-6,99; 12,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 22,12</t>
+          <t>-15,64; 17,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 25,15</t>
+          <t>-6,99; 24,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 17,11</t>
+          <t>-21,42; 15,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 20,41</t>
+          <t>-10,55; 21,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 32,06</t>
+          <t>-18,73; 25,11</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-49,54</t>
+          <t>-46,35</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-66,88%</t>
+          <t>-63,35%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,36; -0,94</t>
+          <t>-27,13; 0,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 21,72</t>
+          <t>-8,91; 21,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 20,39</t>
+          <t>-9,12; 19,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,89; -24,8</t>
+          <t>-67,52; -17,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,36; -1,81</t>
+          <t>-40,27; 0,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 63,73</t>
+          <t>-18,99; 59,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 42,9</t>
+          <t>-14,33; 39,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-87,87; -36,04</t>
+          <t>-85,22; -24,99</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-6,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-6,24%</t>
+          <t>-8,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 7,13</t>
+          <t>-1,34; 6,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 8,36</t>
+          <t>-0,78; 7,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,37</t>
+          <t>-5,36; 3,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 4,09</t>
+          <t>-15,82; 2,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 11,13</t>
+          <t>-2,0; 10,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 17,89</t>
+          <t>-1,56; 16,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 5,32</t>
+          <t>-7,95; 5,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 5,62</t>
+          <t>-20,6; 3,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2601_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,38</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-11,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-16,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-5,59%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.50530301089219</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10.38111195366923</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-11.57584524288079</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.394735276959782</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.03739400270503945</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.2215987746910283</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.164487030224427</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.05592618281031907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,81; 12,57</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,71; 21,7</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-24,05; 0,36</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-23,57; 13,14</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-10,78; 20,87</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 52,75</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-32,82; -0,21</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-27,21; 18,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.811326133690442</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.708986709127734</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-24.04556018489249</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-23.56860125808452</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1078250772642798</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.04859599539495624</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3281572706929513</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2720832388628677</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.5737178034604</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21.70238392783882</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3576167626928274</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.14014066597441</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.208698222380644</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.5275050357367612</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-0.002060199698938234</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1851021342023799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13,76</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,47</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-16,79</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,07%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-21,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,75; 12,8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3,31; 24,68</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,91; 20,53</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-37,62; 4,15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-9,99; 18,94</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,57; 53,29</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-1,4; 37,74</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-44,91; 6,3</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.749259729164477</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>13.76293339336846</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9.467039313380909</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-16.78699266319465</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.03750458948367339</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2585083359923372</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1607072617936925</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2156516749531248</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,16</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-15,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,83</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-22,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.748473453984873</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3.311397360484644</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.9094281144322612</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-37.62499387720838</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.0998699414692313</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.05565323655939385</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.01399462854546915</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.449133893042596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,6; 15,56</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-12,97; 13,58</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-29,54; -3,62</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-24,99; 39,64</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-12,56; 28,41</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-22,81; 32,89</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-38,62; -5,98</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-40,67; 113,08</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12.79980285697972</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>24.68029790501745</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>20.52953171509731</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.153184676756088</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1893793632825992</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.53291870016068</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.3773596206948774</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.06295602323037658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.158218602994822</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.158244915057526</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-15.97307782725058</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>11.83126908928298</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.05077936566755181</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.003226114383165001</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2225771572760943</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2446112327652437</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,79; 15,08</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,21; 9,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 6,21</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-14,91; 17,86</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,07; 25,83</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-11,94; 22,7</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-11,96; 10,12</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-18,54; 26,67</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.603980239108212</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-12.97165484780917</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-29.53642394979518</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-24.99110179105989</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1255510309348392</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2281215592399613</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3862438639195995</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4067234275414166</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>15.56264249241161</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.57622900448446</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-3.62163849299147</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>39.64298450923044</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2841141317020718</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3288773087414496</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-0.059752362726694</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.13082471191069</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,63</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,51</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-4,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-4,84; 14,79</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,07; 7,45</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,99; 12,29</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-15,64; 17,76</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-6,99; 24,39</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-21,42; 15,35</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-10,55; 21,45</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,73; 25,11</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>8.092870682884513</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.145041303128064</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.670382459741326</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.462075819018061</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1301333452609719</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.02356619620554939</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02540051322740864</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.03252513881339616</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-14,02</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6,33</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5,71</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-46,35</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-22,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-63,35%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7928868948428751</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.214962670249178</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-8.251478567678488</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-14.91104069939599</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.01070456256683715</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1193595827743587</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1196234436547066</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1854236027510912</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-27,13; 0,13</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,91; 21,14</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-9,12; 19,21</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-67,52; -17,18</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-40,27; 0,38</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-18,99; 59,83</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-14,33; 39,42</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-85,22; -24,99</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>15.08417235462538</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.837825991608804</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.210827807187375</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>17.85990780469913</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2582566168771984</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2269687600594244</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1012484669389794</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2667413839179868</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,86</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-6,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-1,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-8,78%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>4.629716090335078</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.510467045846798</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.019788202746842</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.136516012290768</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.07160139578999052</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.04772982079712465</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03213154378153067</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.02743186706402325</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 6,83</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,78; 7,99</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; 3,14</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-15,82; 2,22</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,0; 10,83</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 16,98</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-7,95; 5,03</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-20,6; 3,06</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.841186537105759</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-12.06614894196209</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.98899472804035</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-15.63774879042587</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.06991612639992681</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2141984665923093</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1055220897087229</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1873029656637477</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.78737253483352</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.449364207298742</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>12.28591733848238</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>17.76307160284619</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2439496353786134</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1535375032725566</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.214523510061369</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2511051939804303</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-14.02438074676267</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>6.331612452712903</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5.70842746582263</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-46.34912277745542</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.227016154401758</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1569218236240316</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.1002310674571842</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.6335061606657505</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-27.12571842667425</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.906616776810425</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-9.121668951193877</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-67.52252892630004</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.402675176670627</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1899250195959994</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.1433421296784872</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.8521848679986681</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.1282745218488651</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>21.13791999656222</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>19.21311974418843</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-17.17872194928039</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.003809551172913998</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.598278269553543</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.3941929590642222</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-0.2498893734767023</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.858259434158172</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.809263074020797</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.134717173870881</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-6.516289938597552</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.04416721989375712</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.07771013577855655</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.01759026396750146</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.08780894588580228</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.339915717530027</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.7795366827201811</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-5.360697063271338</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-15.81916021436637</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.01999453814982171</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.01556328503486619</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.07951713991404352</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.2060033154264914</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.825079199730137</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>7.994151968608379</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.138463278640464</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.222311550101257</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.1083327986119491</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.1698378957435268</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.05033595894958217</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.03056342408378601</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
